--- a/php/Inventaris.xlsx
+++ b/php/Inventaris.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
-    <sheet name="Namen" sheetId="2" r:id="rId5"/>
+    <sheet name="kieken" sheetId="2" r:id="rId5"/>
+    <sheet name="Namen" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -482,4 +483,79 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.141" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10.569" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.711" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
 </file>